--- a/sheets/대금율보/검수/남원산성.xlsx
+++ b/sheets/대금율보/검수/남원산성.xlsx
@@ -10452,32 +10452,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -10681,7 +10681,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -11245,7 +11245,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -11508,7 +11508,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -11584,10 +11584,10 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -12407,7 +12407,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -12645,10 +12645,10 @@
       </c>
       <c r="U28" s="24"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="80.0" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="119.22" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -12746,7 +12746,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="119.22" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="23"/>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="119.22" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="24"/>
@@ -12874,7 +12874,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="119.22" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
@@ -12938,7 +12938,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="119.22" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -13002,7 +13002,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="119.22" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -13052,7 +13052,7 @@
       <c r="T36" s="21"/>
       <c r="U36" s="24"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="119.22" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
@@ -13126,7 +13126,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="119.22" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="23"/>
@@ -13181,7 +13181,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="119.22" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="24"/>
@@ -13221,7 +13221,7 @@
       <c r="T39" s="21"/>
       <c r="U39" s="24"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="119.22" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="22"/>
@@ -13294,7 +13294,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="119.22" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="23"/>
@@ -13321,7 +13321,7 @@
       <c r="T41" s="21"/>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="119.22" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="24"/>
@@ -13385,7 +13385,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
